--- a/www/download/IND.hours_worked.empe_ms.r.pc.rpA1.xlsx
+++ b/www/download/IND.hours_worked.empe_ms.r.pc.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>0.348362937765847</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>35.09</t>
+          <t>0.350930694736798</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>35.37</t>
+          <t>0.353661187586671</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>0.356573334821328</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>35.97</t>
+          <t>0.359688922457053</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>0.363033185664254</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>36.66</t>
+          <t>0.366635535000485</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.55</t>
+          <t>0.365531045509784</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>36.48</t>
+          <t>0.364773902744126</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>37.94</t>
+          <t>0.37936587381734</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.393915984583342</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.393915984583342</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.393915984583342</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.393915984583342</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>0.393915984583342</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>66.74</t>
+          <t>0.667441399753227</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>67.97</t>
+          <t>0.67965633652255</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>68.69</t>
+          <t>0.686852596963825</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>0.682352512144294</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>66.21</t>
+          <t>0.662085467053103</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>0.661808110937379</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>66.86</t>
+          <t>0.668640698699335</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>66.95</t>
+          <t>0.669477251930921</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>67.04</t>
+          <t>0.67036171385888</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>65.46</t>
+          <t>0.654647805504798</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>66.46</t>
+          <t>0.664638824404813</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>66.07</t>
+          <t>0.660742385300573</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>0.65102115522402</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>0.662419824639012</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>66.52</t>
+          <t>0.665221646858623</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>0.458345020135554</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>0.472067124700069</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48.28</t>
+          <t>0.482795676750388</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>49.22</t>
+          <t>0.492247004959802</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>49.99</t>
+          <t>0.499927097718679</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>0.517127740576561</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>52.96</t>
+          <t>0.529645758851097</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>0.538480827969708</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>54.66</t>
+          <t>0.54663524183637</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>56.73</t>
+          <t>0.567256667411875</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>0.578512912924773</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>0.587281382681211</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>59.38</t>
+          <t>0.593824328538605</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>58.74</t>
+          <t>0.587424750347006</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>59.27</t>
+          <t>0.592746490029178</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>0.149374382655247</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>0.155770502716519</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>0.148432965518307</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>0.141043625728438</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>0.152727722560584</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>0.156792418524991</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>0.163142546644421</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>0.162375411188584</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>0.16653267978683</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>0.175757286429952</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>0.179013652283156</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>0.187159780642293</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>0.182028895279162</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>0.18440883981998</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>0.202179913289584</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>0.273601964623949</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>0.285335237123337</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>0.297068509622725</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>0.308801782122114</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>32.05</t>
+          <t>0.320535054621502</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>0.33226832712089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>0.344001599620279</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>0.355734872119667</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>0.370214731055326</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>0.384694589990986</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>39.92</t>
+          <t>0.399174448926646</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>0.41032044478257</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>0.421466440638494</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>43.26</t>
+          <t>0.432612436494418</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>44.38</t>
+          <t>0.443758432350343</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>78.73</t>
+          <t>0.787343230683292</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>78.97</t>
+          <t>0.789704952553665</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.08</t>
+          <t>0.790785016748082</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>78.85</t>
+          <t>0.78853463095468</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>79.55</t>
+          <t>0.795486394695564</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>79.25</t>
+          <t>0.792478849347931</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>0.789518127429825</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.65</t>
+          <t>0.786493111883581</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>78.45</t>
+          <t>0.784531397519799</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>78.37</t>
+          <t>0.783655875464756</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>77.88</t>
+          <t>0.778795042980499</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>0.771378760869917</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>76.74</t>
+          <t>0.76736959997502</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>77.02</t>
+          <t>0.770214247141349</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>0.760021404366665</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>44.08</t>
+          <t>0.440763305854076</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>0.446761572997244</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>45.27</t>
+          <t>0.452663377317704</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>45.85</t>
+          <t>0.458460645622173</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>0.46414528481011</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>46.97</t>
+          <t>0.469709201971289</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>47.51</t>
+          <t>0.475144325035073</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>48.04</t>
+          <t>0.48044262388356</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>47.18</t>
+          <t>0.471814324658347</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>0.461216139244906</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>0.450635553120864</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>0.439953048243381</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>43.57</t>
+          <t>0.435683855712475</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>0.43195168744715</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>0.43195168744715</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>0.359447173559755</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>0.367002576026058</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.81</t>
+          <t>0.358082664819624</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>0.347848501886329</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>37.15</t>
+          <t>0.371520788571168</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>0.377445256022587</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>0.382594963330836</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>0.380685901781172</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>0.390437025126417</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>0.403575019887614</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>0.416900756395004</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>0.428554835823112</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>42.09</t>
+          <t>0.420868018826323</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>42.58</t>
+          <t>0.425813446969654</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>42.93</t>
+          <t>0.429346185139048</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>80.58</t>
+          <t>0.805841222536161</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>80.58</t>
+          <t>0.805841222536161</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.58</t>
+          <t>0.805841222536161</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>80.58</t>
+          <t>0.805841222536161</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>80.48</t>
+          <t>0.804787187220306</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>80.62</t>
+          <t>0.806229363696137</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>80.85</t>
+          <t>0.808486122329607</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>80.98</t>
+          <t>0.809789865320462</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>81.36</t>
+          <t>0.813629861056625</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>0.813023399505688</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>81.68</t>
+          <t>0.816831842181587</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>81.33</t>
+          <t>0.81329555491645</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>81.21</t>
+          <t>0.81212231911831</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>80.65</t>
+          <t>0.806522264713003</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>79.99</t>
+          <t>0.799894088103586</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>63.61</t>
+          <t>0.63606301929354</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>0.637096976669119</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>0.637065756539099</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>63.11</t>
+          <t>0.631067282541124</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>62.81</t>
+          <t>0.628112529655099</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>0.623163264316266</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>0.619472028944092</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>0.618968233794798</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>60.88</t>
+          <t>0.608778533378536</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>60.81</t>
+          <t>0.608101359468275</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>0.599776482128622</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>0.606592253844489</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>61.89</t>
+          <t>0.618927960349674</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>61.97</t>
+          <t>0.619677145111692</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>61.08</t>
+          <t>0.610837209615879</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>54.35</t>
+          <t>0.543535941765506</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>0.547630426112232</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>54.96</t>
+          <t>0.549623609947919</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>55.18</t>
+          <t>0.551822541642323</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>55.53</t>
+          <t>0.555259003591729</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>55.75</t>
+          <t>0.557495429296252</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>55.79</t>
+          <t>0.557887924476222</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>0.55862712331648</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>52.32</t>
+          <t>0.523188138152505</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>51.81</t>
+          <t>0.518107901006387</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>50.05</t>
+          <t>0.500531128762789</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>0.498972650293365</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>0.463064097279716</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>46.28</t>
+          <t>0.462801473471055</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>0.446502858598185</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>0.160151761310241</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>17.13</t>
+          <t>0.1713049132251</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>17.97</t>
+          <t>0.179745371785676</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>18.69</t>
+          <t>0.186945277395556</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>0.192565543844875</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>0.199111439255819</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>19.97</t>
+          <t>0.199713364057565</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>0.20228078575005</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>20.77</t>
+          <t>0.207694714792361</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>0.215276170376725</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>0.231039037491323</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>0.237354213442524</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>0.240328230587112</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>24.16</t>
+          <t>0.241598508970236</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>0.238850083680788</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>58.15</t>
+          <t>0.581542571932428</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>58.86</t>
+          <t>0.588639190261022</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>0.588409307670143</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>58.73</t>
+          <t>0.587257231156354</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>60.77</t>
+          <t>0.60768719805086</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>0.60760353311715</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>60.79</t>
+          <t>0.60792014362135</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>60.47</t>
+          <t>0.60472423075156</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>60.02</t>
+          <t>0.600160104455164</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>59.31</t>
+          <t>0.593090372720958</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>58.51</t>
+          <t>0.585145653993799</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>57.67</t>
+          <t>0.576657993504508</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>58.67</t>
+          <t>0.586727142569739</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>57.98</t>
+          <t>0.579775338458534</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>57.62</t>
+          <t>0.576241107211232</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>0.435316951886601</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>0.441566304892616</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>44.81</t>
+          <t>0.448133256416424</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>0.450608738153833</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>45.61</t>
+          <t>0.456051366651535</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>0.463080981079406</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>0.467042078216123</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>0.471163259919086</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>0.47676111747414</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>0.485667845821841</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>48.79</t>
+          <t>0.487876600547858</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>0.491498400324855</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>48.94</t>
+          <t>0.489432125542819</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>49.09</t>
+          <t>0.490929019346309</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>48.71</t>
+          <t>0.487053716418833</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>43.85</t>
+          <t>0.438506846401866</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.94</t>
+          <t>0.439352238166532</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>0.445126085625454</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>0.452537504695825</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>0.45598823932306</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>46.18</t>
+          <t>0.461772800360354</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>0.466141360726737</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>47.36</t>
+          <t>0.473597165484781</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>47.93</t>
+          <t>0.479294656517124</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>0.477443039611786</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>0.476079743991847</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>0.468049827173135</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>0.475049352150546</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>0.478969206372087</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>46.62</t>
+          <t>0.466181484681819</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>43.32</t>
+          <t>0.433241589076702</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>0.440991399183517</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>0.463079372051525</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>0.463273795379137</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>46.37</t>
+          <t>0.463675712205606</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>0.458116574755566</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>0.449818700886118</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>45.54</t>
+          <t>0.455396582149686</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>47.67</t>
+          <t>0.476733137253857</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>0.491909929449492</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>49.23</t>
+          <t>0.492288182470444</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>0.489822794062092</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>0.468380014306229</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>0.472070456315513</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>47.98</t>
+          <t>0.479810922968492</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>0.355690066285184</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>36.32</t>
+          <t>0.363197207031498</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>37.84</t>
+          <t>0.378439299976295</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>0.393739663077918</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>41.65</t>
+          <t>0.416540282371946</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>0.421060563778224</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>41.84</t>
+          <t>0.418399661683136</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>0.430252042245956</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>0.440702665586576</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>0.458203819898153</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>0.463184319015617</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>41.97</t>
+          <t>0.419702690233041</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>0.420181667462409</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>42.98</t>
+          <t>0.429839901364051</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>42.71</t>
+          <t>0.427056382349114</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>0.677970253379368</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>0.677970253379368</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>0.677970253379368</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>0.677970253379368</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>0.697700742937093</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>68.12</t>
+          <t>0.681231637034883</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>68.36</t>
+          <t>0.683591719541622</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>0.689952099210062</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>69.07</t>
+          <t>0.690699698721832</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>68.27</t>
+          <t>0.682681886601219</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>0.679949049644513</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>0.686344318430707</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>68.93</t>
+          <t>0.68926932743156</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>67.54</t>
+          <t>0.675402957988325</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>68.58</t>
+          <t>0.685755771781092</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>0.225387955959682</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>0.237009789150174</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>24.19</t>
+          <t>0.241919450531589</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25.32</t>
+          <t>0.25317786226604</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>25.47</t>
+          <t>0.254701099488972</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>27.52</t>
+          <t>0.275240379535049</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>0.268840320941189</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>27.38</t>
+          <t>0.273826824067002</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>0.29698568126144</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>0.288957028372602</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>0.290555367595629</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>0.292153706818657</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.281321561177494</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.281321561177494</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>28.13</t>
+          <t>0.281321561177494</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>0.393099495319025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>0.400344820934381</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>40.76</t>
+          <t>0.407590146549737</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>0.414835472165093</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>0.422080797780449</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>0.415736576939963</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>0.409392356099476</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>0.40304813525899</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>0.396703914418503</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>0.390359693578017</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>0.390359693578017</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>0.390359693578017</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>0.390359693578017</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>0.390359693578017</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>0.390359693578017</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>43.33</t>
+          <t>0.433327810946452</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>44.49</t>
+          <t>0.44490994834356</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>0.452400829696932</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>44.73</t>
+          <t>0.447331669379548</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>44.27</t>
+          <t>0.4427128045549</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>0.436900933409306</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>0.427572595839524</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>0.424523639477111</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>0.422019268911282</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>0.409196985907454</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>0.411506251883783</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>0.410382874176191</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>41.06</t>
+          <t>0.410621569332512</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>40.52</t>
+          <t>0.405243912708142</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>0.401421265114714</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>35.67</t>
+          <t>0.356683496787542</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>0.369457860635674</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>0.382425513470241</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>0.394586737653297</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>0.404867465876106</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>42.89</t>
+          <t>0.428904162541322</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>0.408024071566911</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>0.412802153543048</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>0.426547959811869</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>45.13</t>
+          <t>0.451321405838827</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>0.454828719520867</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>0.462073554632459</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>0.463345443318637</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>46.29</t>
+          <t>0.462893831730371</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>0.474074665641196</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>62.22</t>
+          <t>0.622246476399754</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>62.71</t>
+          <t>0.627053672179184</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>0.631624239486648</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>63.51</t>
+          <t>0.63506489558648</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>63.89</t>
+          <t>0.638928365464984</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>64.27</t>
+          <t>0.642706358372937</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>64.52</t>
+          <t>0.645156589217239</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>64.29</t>
+          <t>0.642938041798118</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>64.94</t>
+          <t>0.649415935630278</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>64.76</t>
+          <t>0.647633825048664</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>64.69</t>
+          <t>0.646865558821761</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>64.69</t>
+          <t>0.646865558821761</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>64.69</t>
+          <t>0.646865558821761</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>64.69</t>
+          <t>0.646865558821761</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>64.69</t>
+          <t>0.646865558821761</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>46.89</t>
+          <t>0.468885762181886</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>0.46768117868951</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>0.470119431690414</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>46.59</t>
+          <t>0.465859789604328</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>45.99</t>
+          <t>0.459922710933326</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>46.76</t>
+          <t>0.467590107354008</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>0.467462732560993</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>0.456048864718562</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>0.455280579791477</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>46.21</t>
+          <t>0.462053049660315</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.459232263808909</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.459232263808909</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.459232263808909</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.459232263808909</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>45.92</t>
+          <t>0.459232263808909</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>64.62</t>
+          <t>0.646228047280277</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>0.652627353480906</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>65.31</t>
+          <t>0.653107348417245</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>65.26</t>
+          <t>0.652594632124127</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>67.01</t>
+          <t>0.670062556504154</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>67.09</t>
+          <t>0.670949445669624</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>0.671623283553242</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>66.81</t>
+          <t>0.668130510696502</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>65.69</t>
+          <t>0.656894682280306</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>0.65300956755162</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>64.67</t>
+          <t>0.646707543985714</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>64.47</t>
+          <t>0.644679842235686</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>62.39</t>
+          <t>0.623911083320607</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>63.36</t>
+          <t>0.633630615149237</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>62.4</t>
+          <t>0.623970896490178</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>32.01</t>
+          <t>0.32007427466936</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>33.18</t>
+          <t>0.331826193733228</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>0.38100036497172</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>0.430793214006936</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>0.478430059071846</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>0.47083555952887</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>0.463212186570251</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>46.23</t>
+          <t>0.46227552482524</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>0.475962323149365</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>0.448918047467116</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>0.444550979740482</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>46.08</t>
+          <t>0.460759138469995</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>44.21</t>
+          <t>0.442084856965206</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>44.92</t>
+          <t>0.449172959403727</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>46.74</t>
+          <t>0.467396265874686</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>63.61</t>
+          <t>0.636134326408564</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>0.643016147857893</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>0.639034254055017</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>63.35</t>
+          <t>0.633464354881649</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>65.43</t>
+          <t>0.654347644429622</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>65.63</t>
+          <t>0.656315381336742</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>65.89</t>
+          <t>0.658893951101241</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>65.77</t>
+          <t>0.65766276242967</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>67.63</t>
+          <t>0.676271119393828</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>66.51</t>
+          <t>0.665136407929561</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>66.73</t>
+          <t>0.667321460850943</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>66.71</t>
+          <t>0.667125102185177</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>64.09</t>
+          <t>0.640875307759502</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>62.22</t>
+          <t>0.622209834050845</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>63.32</t>
+          <t>0.633193878189163</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>43.55</t>
+          <t>0.435534505695659</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>0.435002126718</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>0.461029029927319</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>45.68</t>
+          <t>0.456803457345362</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>0.456650281195226</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>45.61</t>
+          <t>0.456126335582338</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>47.15</t>
+          <t>0.4715419419924</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>0.476236168159158</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>48.57</t>
+          <t>0.485696250218827</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>0.499376101496398</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>50.33</t>
+          <t>0.503320194685757</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>51.53</t>
+          <t>0.515255118871448</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>51.53</t>
+          <t>0.515255118871448</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>51.53</t>
+          <t>0.515255118871448</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>51.53</t>
+          <t>0.515255118871448</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>0.149374382655247</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>0.155770502716519</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>0.148432965518307</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>0.141043625728438</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>0.152727722560584</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>0.156792418524991</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>0.163142546644421</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>0.162375411188584</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>0.16653267978683</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>0.175757286429952</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>0.179013652283156</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>0.187159780642293</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>0.182028895279162</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>0.18440883981998</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>0.202179913289584</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>46.73</t>
+          <t>0.467334020449806</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>0.473177590563234</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>0.466075156318148</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>46.73</t>
+          <t>0.467285928622662</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>0.464069182841793</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>0.438559146158021</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>44.34</t>
+          <t>0.443410457536547</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>45.93</t>
+          <t>0.459312454396778</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>44.78</t>
+          <t>0.447784685215382</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>0.445202107804114</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>44.64</t>
+          <t>0.446375978076828</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>0.446730278361894</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>0.453618787929575</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>0.436687487587405</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>0.433783964126723</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>0.776542665775152</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>0.776542665775152</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>0.776542665775152</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>0.776542665775152</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>0.776542665775152</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>77.65</t>
+          <t>0.776542665775152</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>0.766039863441556</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.64</t>
+          <t>0.766362663654355</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>76.03</t>
+          <t>0.760297201690192</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>0.746768404993518</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>74.06</t>
+          <t>0.740576730084175</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>73.47</t>
+          <t>0.734687391152289</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>0.728261829122457</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>0.723964954159925</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>0.70997595536251</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>0.149374382655247</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>0.155770502716519</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>0.148432965518307</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>0.141043625728438</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>0.152727722560584</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>0.156792418524991</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>0.163142546644421</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>0.162375411188584</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>0.16653267978683</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>0.175757286429952</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>0.179013652283156</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>0.187159780642293</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>0.182028895279162</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>0.18440883981998</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>0.202179913289584</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>0.149374382655247</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>0.155770502716519</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>0.148432965518307</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>0.141043625728438</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>0.152727722560584</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>0.156792418524991</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>0.163142546644421</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>0.162375411188584</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>0.16653267978683</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>0.175757286429952</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>0.179013652283156</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>0.187159780642293</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>0.182028895279162</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>0.18440883981998</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>0.202179913289584</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>77.69</t>
+          <t>0.776895446467441</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>77.69</t>
+          <t>0.776895446467441</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>77.69</t>
+          <t>0.776895446467441</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>77.69</t>
+          <t>0.776895446467441</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>77.57</t>
+          <t>0.775681700683508</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>77.73</t>
+          <t>0.777297968829515</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>77.98</t>
+          <t>0.779820603452676</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>78.13</t>
+          <t>0.781325829321574</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>78.47</t>
+          <t>0.784707910168885</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>0.788673148182128</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>0.789901518333299</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>0.789901518333299</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>0.789901518333299</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>0.789901518333299</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>78.99</t>
+          <t>0.789901518333299</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>79.97</t>
+          <t>0.799744870939769</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>79.97</t>
+          <t>0.799744870939769</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>79.97</t>
+          <t>0.799744870939769</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>79.97</t>
+          <t>0.799744870939769</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>82.21</t>
+          <t>0.822078293684542</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>82.87</t>
+          <t>0.828733400228587</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>82.95</t>
+          <t>0.829467437184487</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>83.53</t>
+          <t>0.835307999257341</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>0.831442319362502</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>82.71</t>
+          <t>0.82708466204088</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>0.818013188934133</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>81.28</t>
+          <t>0.812790311137944</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>81.51</t>
+          <t>0.81512106377372</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>0.813971932958152</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>0.811104377949596</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>66.96</t>
+          <t>0.669597536849742</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>66.96</t>
+          <t>0.669597536849742</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>66.96</t>
+          <t>0.669597536849742</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>66.96</t>
+          <t>0.669597536849742</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>67.97</t>
+          <t>0.679689624684062</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>66.73</t>
+          <t>0.66734478186268</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>67.95</t>
+          <t>0.679472906294703</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>0.678961289278051</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>66.69</t>
+          <t>0.666898397724071</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>66.61</t>
+          <t>0.666051242258056</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>66.58</t>
+          <t>0.665832069252872</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>66.35</t>
+          <t>0.663491474463731</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>65.87</t>
+          <t>0.658672057320843</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>65.14</t>
+          <t>0.651355114958407</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>0.643975098581195</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>58.57</t>
+          <t>0.585702966243725</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>0.591529283873456</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>0.597372678209279</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>60.24</t>
+          <t>0.602366870709266</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>59.43</t>
+          <t>0.594291764382177</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>60.73</t>
+          <t>0.607277147009464</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>60.91</t>
+          <t>0.609096810665625</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>0.610223712014477</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>61.48</t>
+          <t>0.614762393708153</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>61.25</t>
+          <t>0.612470415297403</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>60.96</t>
+          <t>0.609644581664782</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>60.36</t>
+          <t>0.603618796500982</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>0.603726782905289</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>0.598529920241151</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>0.566309634240847</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>20.99</t>
+          <t>0.209931007375724</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>0.219362923238092</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>22.03</t>
+          <t>0.220271080232369</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>23.21</t>
+          <t>0.232052984924666</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>23.04</t>
+          <t>0.230352419444745</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>0.238998120408275</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>0.244037419803938</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>0.250117256113195</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>0.258896292167912</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>0.258298378554924</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>0.262183090935955</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>0.264231729578054</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>0.273623881762886</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>0.278684828921563</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>28.37</t>
+          <t>0.283745776080239</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>0.3227469521659</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>0.32697344651853</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>33.12</t>
+          <t>0.33119994087116</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>33.54</t>
+          <t>0.335426435223791</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>0.339652929576421</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>34.39</t>
+          <t>0.343879423929051</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>0.348105918281681</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>35.23</t>
+          <t>0.352332412634311</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>35.27</t>
+          <t>0.352659077651124</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>0.352985742667937</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>0.35040809984152</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>34.52</t>
+          <t>0.345171811253209</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>35.13</t>
+          <t>0.351305333899944</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>0.351708638479808</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>35.75</t>
+          <t>0.357530055963773</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>64.42</t>
+          <t>0.644182234776234</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>64.89</t>
+          <t>0.648892437876221</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>64.14</t>
+          <t>0.641396686981481</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>64.45</t>
+          <t>0.644486321916615</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>0.639986161568194</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>64.25</t>
+          <t>0.642458079769947</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>63.86</t>
+          <t>0.638582952099535</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>63.15</t>
+          <t>0.631547031092499</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>0.631359293288519</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>0.629551079491841</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>62.98</t>
+          <t>0.629840257277529</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>62.52</t>
+          <t>0.625214446030152</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>63.09</t>
+          <t>0.630852286123446</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>62.9</t>
+          <t>0.629026818574473</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>62.67</t>
+          <t>0.62670060370545</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>0.469773565988899</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>0.475494398270178</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>0.479710527481293</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>0.482224189295601</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>48.92</t>
+          <t>0.489192905849045</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>0.491557547666794</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>49.29</t>
+          <t>0.49292446743076</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>49.46</t>
+          <t>0.494602048512791</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>49.68</t>
+          <t>0.496828174229481</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>0.4980998533911</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>0.498983843039248</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>0.499095031787207</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>0.496367579988465</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>0.49598976431317</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>0.496499581531323</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>0.469773565988899</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>47.55</t>
+          <t>0.475494398270178</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>0.479710527481293</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>48.22</t>
+          <t>0.482224189295601</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>48.92</t>
+          <t>0.489192905849045</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>49.16</t>
+          <t>0.491557547666794</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>49.29</t>
+          <t>0.49292446743076</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>49.46</t>
+          <t>0.494602048512791</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>49.68</t>
+          <t>0.496828174229481</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>0.4980998533911</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>0.498983843039248</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>0.499095031787207</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>0.496367579988465</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>0.49598976431317</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>0.496499581531323</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>hours_worked.empe_ms.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
